--- a/output/pdf_financials_xlsx/DEFI.xlsx
+++ b/output/pdf_financials_xlsx/DEFI.xlsx
@@ -553,10 +553,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>2.857343</v>
+        <v>41.129044</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>4.662247</v>
+        <v>27.35144</v>
       </c>
     </row>
     <row r="11">
@@ -566,10 +566,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>18.919832</v>
+        <v>-19.351869</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>52.419088</v>
+        <v>29.729895</v>
       </c>
     </row>
     <row r="12">
@@ -4638,7 +4638,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E92" s="5" t="n">

--- a/output/pdf_financials_xlsx/DEFI.xlsx
+++ b/output/pdf_financials_xlsx/DEFI.xlsx
@@ -819,10 +819,10 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0</v>
+        <v>0.759141</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>0.705441</v>
       </c>
     </row>
     <row r="29">
@@ -1771,10 +1771,10 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.759141</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.705441</v>
       </c>
     </row>
     <row r="101">
@@ -3260,7 +3260,11 @@
           <t>Amortization - Intangible asset 9</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E38" s="5" t="n">
         <v>0.759141</v>
       </c>
